--- a/artfynd/A 16767-2023 artfynd.xlsx
+++ b/artfynd/A 16767-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16767-2023 artfynd.xlsx
+++ b/artfynd/A 16767-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17277788</v>
+        <v>17277813</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605996.612749481</v>
+        <v>605997</v>
       </c>
       <c r="R2" t="n">
-        <v>6970657.324458244</v>
+        <v>6970657</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -752,19 +747,9 @@
           <t>2012-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,42 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17277813</v>
+        <v>17278262</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605996.612749481</v>
+        <v>605997</v>
       </c>
       <c r="R3" t="n">
-        <v>6970657.324458244</v>
+        <v>6970657</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +857,9 @@
           <t>2012-07-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,42 +895,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17277837</v>
+        <v>17277788</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605996.612749481</v>
+        <v>605997</v>
       </c>
       <c r="R4" t="n">
-        <v>6970657.324458244</v>
+        <v>6970657</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1002,19 +967,9 @@
           <t>2012-07-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-07-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1005,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17278262</v>
+        <v>17277837</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605996.612749481</v>
+        <v>605997</v>
       </c>
       <c r="R5" t="n">
-        <v>6970657.324458244</v>
+        <v>6970657</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1127,19 +1077,9 @@
           <t>2012-07-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-07-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16767-2023 artfynd.xlsx
+++ b/artfynd/A 16767-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277813</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278262</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>